--- a/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 21,51</t>
+          <t>17,44; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 19,74</t>
+          <t>17,05; 19,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 21,29</t>
+          <t>16,96; 20,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 20,4</t>
+          <t>16,37; 20,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 23,61</t>
+          <t>18,13; 23,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,75; 21,61</t>
+          <t>16,72; 21,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 18,48</t>
+          <t>16,53; 18,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 18,27</t>
+          <t>15,82; 18,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 22,08</t>
+          <t>18,28; 21,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 19,8</t>
+          <t>17,21; 19,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 19,48</t>
+          <t>17,07; 19,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 18,88</t>
+          <t>16,37; 18,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 18,26</t>
+          <t>17,36; 18,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 18,38</t>
+          <t>17,32; 18,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 18,14</t>
+          <t>16,94; 18,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,96; 18,5</t>
+          <t>16,91; 18,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 19,57</t>
+          <t>17,98; 19,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 20,15</t>
+          <t>18,51; 20,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 19,09</t>
+          <t>17,63; 19,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 19,4</t>
+          <t>17,32; 19,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,75</t>
+          <t>17,79; 18,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 19,15</t>
+          <t>18,13; 19,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,45</t>
+          <t>17,43; 18,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 18,8</t>
+          <t>17,29; 18,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,53</t>
+          <t>18,57; 19,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 20,58</t>
+          <t>19,4; 20,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,3</t>
+          <t>18,38; 19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,88</t>
+          <t>17,93; 18,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,69; 19,65</t>
+          <t>18,66; 19,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 22,03</t>
+          <t>19,32; 22,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,8</t>
+          <t>18,83; 19,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,4; 19,48</t>
+          <t>18,41; 19,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 19,4</t>
+          <t>18,73; 19,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,98</t>
+          <t>19,51; 21,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,4</t>
+          <t>18,75; 19,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 19,03</t>
+          <t>18,31; 19,04</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,2; 20,85</t>
+          <t>20,21; 20,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 21,5</t>
+          <t>20,33; 21,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 21,06</t>
+          <t>20,1; 21,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 21,19</t>
+          <t>19,52; 21,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 21,82</t>
+          <t>21,17; 21,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 21,61</t>
+          <t>20,73; 21,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 21,01</t>
+          <t>20,09; 21,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 21,3</t>
+          <t>20,05; 21,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 21,22</t>
+          <t>20,79; 21,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 21,38</t>
+          <t>20,66; 21,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 20,83</t>
+          <t>20,24; 20,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,94; 21,0</t>
+          <t>20,04; 21,11</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,3</t>
+          <t>18,76; 19,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,62</t>
+          <t>18,99; 19,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,16</t>
+          <t>18,54; 19,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,62</t>
+          <t>18,57; 19,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,22</t>
+          <t>19,4; 20,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,52</t>
+          <t>19,52; 20,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,51</t>
+          <t>18,79; 19,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 19,79</t>
+          <t>18,9; 19,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,68</t>
+          <t>19,19; 19,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 19,93</t>
+          <t>19,35; 19,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,2</t>
+          <t>18,74; 19,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 19,54</t>
+          <t>18,86; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,11</t>
+          <t>17,47; 21,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 19,72</t>
+          <t>17,08; 19,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 20,95</t>
+          <t>17,05; 20,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 20,6</t>
+          <t>16,44; 20,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 23,73</t>
+          <t>18,35; 24,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 21,5</t>
+          <t>16,77; 21,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,53; 18,39</t>
+          <t>16,46; 18,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,82; 18,18</t>
+          <t>15,84; 18,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,93</t>
+          <t>18,28; 21,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 19,74</t>
+          <t>17,27; 19,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,07; 19,27</t>
+          <t>17,01; 19,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 18,83</t>
+          <t>16,47; 18,94</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 18,3</t>
+          <t>17,34; 18,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 18,41</t>
+          <t>17,3; 18,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 18,2</t>
+          <t>16,9; 18,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 18,56</t>
+          <t>16,94; 18,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,98; 19,57</t>
+          <t>17,96; 19,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,08</t>
+          <t>18,51; 20,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 19,04</t>
+          <t>17,61; 19,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 19,8</t>
+          <t>17,28; 19,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 18,75</t>
+          <t>17,78; 18,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 19,08</t>
+          <t>18,09; 19,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 18,43</t>
+          <t>17,46; 18,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 18,6</t>
+          <t>17,28; 18,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,57; 19,51</t>
+          <t>18,54; 19,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,53</t>
+          <t>19,39; 20,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,37</t>
+          <t>18,42; 19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,93</t>
+          <t>17,88; 18,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,58</t>
+          <t>18,67; 19,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,36</t>
+          <t>19,32; 22,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,83; 19,85</t>
+          <t>18,79; 19,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,46</t>
+          <t>18,33; 19,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,4</t>
+          <t>18,72; 19,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 21,0</t>
+          <t>19,53; 20,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,4</t>
+          <t>18,73; 19,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,31; 19,04</t>
+          <t>18,28; 19,0</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 20,86</t>
+          <t>20,19; 20,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,33; 21,42</t>
+          <t>20,33; 21,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 21,0</t>
+          <t>20,1; 21,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 21,17</t>
+          <t>19,56; 21,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 21,67</t>
+          <t>20,72; 21,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 21,09</t>
+          <t>20,12; 21,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 21,34</t>
+          <t>20,07; 21,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,79; 21,26</t>
+          <t>20,81; 21,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,66; 21,38</t>
+          <t>20,69; 21,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 20,87</t>
+          <t>20,23; 20,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,04; 21,11</t>
+          <t>20,01; 21,06</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,76; 19,34</t>
+          <t>18,72; 19,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,63</t>
+          <t>18,97; 19,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,17</t>
+          <t>18,53; 19,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,57; 19,73</t>
+          <t>18,56; 19,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,19</t>
+          <t>19,46; 20,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 20,45</t>
+          <t>19,55; 20,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,51</t>
+          <t>18,75; 19,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,9; 19,75</t>
+          <t>18,94; 19,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,68</t>
+          <t>19,18; 19,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,92</t>
+          <t>19,35; 19,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,74; 19,2</t>
+          <t>18,73; 19,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,51</t>
+          <t>18,87; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16,87</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,49</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,83</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,31</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,79</t>
+          <t>17,85</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,46</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 21,27</t>
+          <t>18,28; 23,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 19,68</t>
+          <t>16,75; 21,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 20,97</t>
+          <t>16,44; 18,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 20,84</t>
+          <t>16,01; 18,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,35; 24,14</t>
+          <t>17,57; 21,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,77; 21,33</t>
+          <t>17,11; 19,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 18,47</t>
+          <t>17,11; 21,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 18,29</t>
+          <t>16,44; 20,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,55</t>
+          <t>18,32; 22,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 19,84</t>
+          <t>17,25; 19,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 19,26</t>
+          <t>17,05; 19,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,47; 18,94</t>
+          <t>16,44; 19,07</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,18</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,25</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,89</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>17,77</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>17,78</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,41</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,6</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,18</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,25</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>17,32</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,73</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 18,31</t>
+          <t>17,92; 19,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 18,39</t>
+          <t>18,48; 20,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 18,12</t>
+          <t>17,63; 19,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 18,5</t>
+          <t>17,27; 19,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,56</t>
+          <t>17,29; 18,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,04</t>
+          <t>17,3; 18,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 19,07</t>
+          <t>16,95; 18,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,66</t>
+          <t>16,76; 17,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 18,71</t>
+          <t>17,78; 18,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,09; 19,06</t>
+          <t>18,11; 19,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,46; 18,45</t>
+          <t>17,42; 18,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,64</t>
+          <t>17,2; 18,61</t>
         </is>
       </c>
     </row>
@@ -928,44 +928,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,87</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,84</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>18,38</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,13</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,3</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,88</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19,06</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>18,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,57</t>
+          <t>18,69; 19,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,39; 20,52</t>
+          <t>19,33; 22,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,37</t>
+          <t>18,8; 19,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,86</t>
+          <t>18,38; 19,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 19,62</t>
+          <t>18,55; 19,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,1</t>
+          <t>19,35; 20,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,82</t>
+          <t>18,41; 19,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 19,43</t>
+          <t>17,89; 18,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>18,71; 19,4</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19,54; 20,98</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>18,72; 19,4</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19,53; 20,98</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 19,41</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 19,0</t>
+          <t>18,26; 19,02</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20,76</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,85</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20,56</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,49</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,53</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,62</t>
+          <t>20,05</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>20,44</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 20,86</t>
+          <t>21,19; 21,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,33; 21,45</t>
+          <t>20,78; 21,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 21,02</t>
+          <t>20,05; 21,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 21,32</t>
+          <t>20,27; 21,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 21,81</t>
+          <t>20,2; 20,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 21,66</t>
+          <t>20,36; 21,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 21,04</t>
+          <t>20,12; 21,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 21,4</t>
+          <t>19,56; 20,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 21,24</t>
+          <t>20,8; 21,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 21,44</t>
+          <t>20,7; 21,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,23; 20,87</t>
+          <t>20,18; 20,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,01; 21,06</t>
+          <t>20,03; 20,91</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,41</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,82</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>19,12</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,28</t>
+          <t>19,45; 20,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 19,64</t>
+          <t>19,56; 20,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,14</t>
+          <t>18,8; 19,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,66</t>
+          <t>19,06; 19,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 20,24</t>
+          <t>18,75; 19,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,53</t>
+          <t>18,99; 19,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,46</t>
+          <t>18,55; 19,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,94; 19,78</t>
+          <t>18,48; 19,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,66</t>
+          <t>19,18; 19,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,94</t>
+          <t>19,37; 19,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,21</t>
+          <t>18,73; 19,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,51</t>
+          <t>18,87; 19,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,95</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,24</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,49</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17,85</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18,2</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17,91</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,46</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>20.20605198529991</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18.14941044355873</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.30545794429708</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>16.8681783582471</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>18.95308928815417</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>18.23641136078645</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>18.48980957861325</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>17.84545581012573</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>19.66242740764442</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>18.19608926401721</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>17.91457260324385</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>17.45900442156168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>18,28; 23,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16,75; 21,61</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16,44; 18,48</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16,01; 18,46</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17,57; 21,51</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,11; 19,74</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,11; 21,29</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16,44; 20,56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18,32; 22,08</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17,25; 19,8</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17,05; 19,48</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,44; 19,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>18.28431840953928</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16.74807976938355</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>16.44273635719609</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>16.0108733862566</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>17.56641763664664</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>17.11335763409881</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>17.11347067393891</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>16.44045298249867</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18.32181518468391</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>17.25097128849004</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>17.04862840834621</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>16.44113034326836</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>23.61304516039211</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.60919752550753</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>18.48098059169238</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>18.45572010325506</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>21.51187941304363</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>19.74058189999862</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>21.28509266325353</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20.5647794879491</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>22.08037333859509</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>19.79905796423112</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>19.47696081040425</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>19.07185132975735</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>19,18</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,89</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,77</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,78</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17,32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18,18</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18,52</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17,87</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>17,92; 19,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18,48; 20,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17,63; 19,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17,27; 19,36</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,29; 18,26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,3; 18,38</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,95; 18,14</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16,76; 17,91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17,78; 18,75</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18,11; 19,15</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17,42; 18,45</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,2; 18,61</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>18.59868095326661</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>19.1756765350133</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>18.24777338496605</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>17.89373268845615</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>17.77178779729446</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17.77749361384029</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17.41052801038346</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>17.31919719119492</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>18.18322933720678</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>18.51971938079704</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>17.8715729933025</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>17.62585903312354</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>20,13</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,87</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,93</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,84</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,38</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19,06</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20,03</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19,07</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>17.91821430189307</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>18.47957497788422</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>17.62987425751006</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>17.27290417956477</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>17.28547341852692</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>17.30285244651106</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>16.94867656809454</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>16.76029177484416</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>17.77812612918046</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>18.10756802436319</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>17.4225200677867</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>17.19829038101003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 19,65</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>19,33; 22,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>18,38; 19,46</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,55; 19,53</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>19,35; 20,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,41; 19,3</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17,89; 18,88</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18,71; 19,4</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19,54; 20,98</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>18,72; 19,4</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>18,26; 19,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>19.56688082062027</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>20.14673964796177</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>19.08619030568997</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>19.3552493189518</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>18.26147175122464</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>18.38485623110343</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18.13687864826524</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>17.90944519565849</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18.74549791868568</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>19.14570788665893</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>18.45391853726264</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>18.60569656979677</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>21,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20,53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,76</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,85</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20,05</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21,02</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21,01</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20,55</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,44</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>19.1070910726695</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>20.12828417395727</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>19.30160674519279</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>18.86763221303707</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>19.00779976675336</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>19.93076652863213</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>18.83908101780891</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>18.37595058596261</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19.05910771060117</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>20.03059990628563</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>19.07103735648683</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>18.6324981823536</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21,19; 21,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20,78; 21,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20,05; 21,01</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20,27; 21,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,2; 20,85</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,36; 21,5</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,12; 21,06</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19,56; 20,7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20,8; 21,22</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20,7; 21,38</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>20,18; 20,83</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,03; 20,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>18.69082440146383</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>19.33040033472959</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>18.80230120088263</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>18.38382513963064</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.55309920459923</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>19.35490596815971</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>18.4137120895703</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>17.89498621566627</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>18.71478424488896</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>19.5358203711218</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>18.72346523076175</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>18.25930672471991</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19.65129145913341</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.02883160822159</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.79551933027078</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.46012546788785</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19.52534340285973</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20.58424342713348</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.30375612181938</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>18.88397374651273</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>19.39563451541258</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>20.98350249011003</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>19.39842966234395</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>19.01938105818584</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>21.48634993240912</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>21.15557283132385</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20.52660798949921</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>20.76474568468136</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>20.51863927507944</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>20.85195873364575</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>20.5638573419803</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>20.05299430325825</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>21.0165430735485</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21.00596106652811</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>20.54530859989361</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>20.43584251306828</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>21.19495683436369</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>20.77993540215155</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>20.05214291252562</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>20.26610298199586</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>20.19908883069591</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>20.35837031084485</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>20.12016513316375</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>19.55719341549937</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>20.80162839894426</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>20.69892886393622</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>20.18242213691727</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>20.03344723932769</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>21.82129856064183</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.60905843907242</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>21.01291114985441</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>21.49241189086961</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>20.84887954652287</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>21.50137376921087</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>21.05605420909098</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>20.70471330768473</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>21.22354806654589</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>21.37901299302234</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>20.83101628461093</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>20.91001277685784</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,29</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,82</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18,8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19,45; 20,22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19,56; 20,52</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,51</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19,06; 19,89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,75; 19,3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,99; 19,62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,55; 19,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18,48; 19,16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 19,68</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19,37; 19,93</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 19,2</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 19,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>19.7837111511778</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>19.94200608123299</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>19.10766551521962</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>19.40675793458474</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>19.00870532088818</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>19.2863330261248</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>18.82493221474763</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>18.80349289378798</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19.40517326971147</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>19.62311870058403</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>18.97125170427613</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>19.12146496951738</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>19.44555463527815</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>19.55537650236031</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>18.80035537625711</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>19.06347902053687</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>18.74685702743109</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18.98891526856099</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>18.55349939543848</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>18.47961987585568</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19.17947951219681</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19.3721402912312</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>18.72806457421745</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>18.8652289471682</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>20.22230863420729</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>20.52483129221245</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>19.50517297894157</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>19.88734830565901</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.2959412618326</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19.61634376037163</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>19.16249397821689</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>19.16370767472501</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>19.67735933811362</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>19.92649567862192</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>19.19865690315783</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>19.44482765185813</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Edad-trans_orig.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
